--- a/data/numeric/input/old_data_101/1P00265-09_20240901_200846_19#-R.xlsx
+++ b/data/numeric/input/old_data_101/1P00265-09_20240901_200846_19#-R.xlsx
@@ -8247,13 +8247,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{991BF9A5-8E00-45AB-A31D-5AC1DD0B2569}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A00D9F7-A8CB-44AE-A14D-8F7B6DF95F34}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2047234-BC5D-471F-9FBB-91F5CF4A4144}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37729570-38FE-4E2C-AFE3-77CE7991FB46}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B633DE7-4E48-478E-B64D-8A1E3B3AD560}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5FF3B58-DEF5-4CC0-B7BD-688EA3E08C7D}"/>
 </file>